--- a/out/LSTM_Base_repeat_4_000008.xlsx
+++ b/out/LSTM_Base_repeat_4_000008.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.520943964793116</v>
+        <v>8.62785843586423</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.520943964793116</v>
+        <v>8.62785843586423</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.305315212968727</v>
+        <v>9.227858435864231</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.905315212968727</v>
+        <v>0.0804624974787484</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.905315212968727</v>
+        <v>0.0804624974787484</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.9209439647931161</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.305315212968727</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.905315212968727</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.905315212968727</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.905315212968727</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.905315212968727</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.9209439647931161</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.305315212968727</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.305315212968727</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.905315212968727</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.905315212968727</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.905315212968727</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.905315212968727</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.905315212968727</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.905315212968727</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.905315212968727</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.305315212968727</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.305315212968727</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.305315212968727</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.305315212968727</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.305315212968727</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.305315212968727</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.305315212968727</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.305315212968727</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.305315212968727</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.305315212968727</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.305315212968727</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.305315212968727</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.305315212968727</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.305315212968727</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.305315212968727</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.305315212968727</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001297736013130052</v>
+        <v>-8.814955669618211e-05</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1490849425910108</v>
+        <v>-0.1012669099610395</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.305315212968727</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1492147161923238</v>
+        <v>-0.1013550595177356</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1492147161923238</v>
+        <v>-0.1013550595177356</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1492147161923238</v>
+        <v>-0.1013550595177356</v>
       </c>
     </row>
     <row r="49">
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1492147161923238</v>
+        <v>-0.1013550595177356</v>
       </c>
     </row>
     <row r="50">
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1492147161923238</v>
+        <v>-0.1013550595177356</v>
       </c>
     </row>
     <row r="51">
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1492147161923238</v>
+        <v>-0.1013550595177356</v>
       </c>
     </row>
     <row r="52">
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1492147161923238</v>
+        <v>-0.1013550595177356</v>
       </c>
     </row>
     <row r="53">
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1492147161923238</v>
+        <v>-0.1013550595177356</v>
       </c>
     </row>
     <row r="54">
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1492147161923238</v>
+        <v>-0.1013550595177356</v>
       </c>
     </row>
     <row r="55">
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.905315212968727</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1492147161923238</v>
+        <v>-0.1013550595177356</v>
       </c>
     </row>
     <row r="56">
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.905315212968727</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1492147161923238</v>
+        <v>-0.1013550595177356</v>
       </c>
     </row>
     <row r="57">
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.905315212968727</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1492147161923238</v>
+        <v>-0.1013550595177356</v>
       </c>
     </row>
     <row r="58">
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.905315212968727</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1492147161923238</v>
+        <v>-0.1013550595177356</v>
       </c>
     </row>
     <row r="59">
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.905315212968727</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1493406846643996</v>
+        <v>-0.1014331470223259</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.4529536807016031</v>
+        <v>0.280784626064627</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>1.905315212968727</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.7574368788712351</v>
+        <v>0.4606757363498385</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.03227289123594728</v>
+        <v>0.0200058822409753</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>1.905315212968727</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.3683018789041531</v>
+        <v>0.2194519510909577</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.05659565517241828</v>
+        <v>0.03508337270451147</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>1.905315212968727</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.4492095277998231</v>
+        <v>0.2696063947709515</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.06875703714065395</v>
+        <v>0.042622466309079</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.5301225618021029</v>
+        <v>0.31976435981928</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01819466973549165</v>
+        <v>0.01127882762152322</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.4976674099823667</v>
+        <v>0.2996452760272641</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.01010820928558883</v>
+        <v>0.006264118489158451</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.305315212968727</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.4996715478632213</v>
+        <v>0.3008857286902564</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.02123832524175756</v>
+        <v>0.01316483409892891</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.305315212968727</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.5320529712864884</v>
+        <v>0.320958103300164</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.008340508345151199</v>
+        <v>0.005168706523071533</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.905315212968727</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.5274782221804594</v>
+        <v>0.3181203424127828</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.005939126475807337</v>
+        <v>0.003679461448730259</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.5310112779026499</v>
+        <v>0.3203084030693702</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.00233464653561096</v>
+        <v>0.001445227800367095</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.5297368183078358</v>
+        <v>0.3195165296815226</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001322156736795153</v>
+        <v>0.0008181146311830566</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.5300466643403841</v>
+        <v>0.3197066860844351</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0005011531384238221</v>
+        <v>0.0003085565845920197</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.5297242102800717</v>
+        <v>0.319505026608557</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.000231706495334477</v>
+        <v>0.0001414277389743509</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.5296872118031967</v>
+        <v>0.3194802041705244</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>8.219113179022926e-05</v>
+        <v>4.909079472171628e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.5296185871245453</v>
+        <v>0.3194357333050648</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>2.075723058958612e-05</v>
+        <v>1.074052980474707e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.5295778273798234</v>
+        <v>0.3194085493913081</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>7.878615294793062e-06</v>
+        <v>3.108757778203038e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.5295728072744883</v>
+        <v>0.3194035367323935</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>1.677971888793091e-06</v>
+        <v>-8.904788376657899e-07</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.5295687892301446</v>
+        <v>0.3193991551468328</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-1.195152058104458e-07</v>
+        <v>-2.211151546177397e-06</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.5295663545599538</v>
+        <v>0.3193958047920401</v>
       </c>
     </row>
     <row r="78">
@@ -62943,7 +62943,7 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>-3.128590021429696e-06</v>
+        <v>-3.752393347619798e-06</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.5295608373179641</v>
+        <v>0.3193904354650522</v>
       </c>
     </row>
     <row r="79">
@@ -63738,7 +63738,7 @@
         <v>0</v>
       </c>
       <c r="IY79" t="n">
-        <v>-4.413072433009741e-06</v>
+        <v>-4.70653621650487e-06</v>
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.5295545133239562</v>
+        <v>0.3193844427316219</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.5295491455353778</v>
+        <v>0.3193790749430435</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.5295491822838695</v>
+        <v>0.3193791116915352</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.529549292529345</v>
+        <v>0.3193792219370107</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.5295493660263286</v>
+        <v>0.3193792954339944</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.905315212968727</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.5295495497687878</v>
+        <v>0.3193794791764535</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.905315212968727</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.5295510932054442</v>
+        <v>0.31938102261311</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.905315212968727</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.5295525631451173</v>
+        <v>0.3193824925527831</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.905315212968727</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.5295538125938394</v>
+        <v>0.3193837420015051</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.905315212968727</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.5295551722880367</v>
+        <v>0.3193851016957024</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>1.905315212968727</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.5295529673785274</v>
+        <v>0.3193828967861931</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.9209439647931161</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.5295525631451173</v>
+        <v>0.3193824925527831</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.5295517179298054</v>
+        <v>0.3193816473374712</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.5295522691571827</v>
+        <v>0.3193821985648484</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.5295519384207562</v>
+        <v>0.319381867828422</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.5295516444328218</v>
+        <v>0.3193815738404875</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.5295517179298054</v>
+        <v>0.3193816473374712</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.5295512769479035</v>
+        <v>0.3193812063555692</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.5295511667024279</v>
+        <v>0.3193810961100936</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.5295511299539362</v>
+        <v>0.3193810593616019</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.5295512769479035</v>
+        <v>0.3193812063555692</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.5295507992175098</v>
+        <v>0.3193807286251755</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>1.905315212968727</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.5295517546782971</v>
+        <v>0.3193816840859628</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.9209439647931161</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.5295517179298054</v>
+        <v>0.3193816473374712</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.9209439647931161</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.529551387193379</v>
+        <v>0.3193813166010447</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.5295518281752809</v>
+        <v>0.3193817575829467</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.5295512034509199</v>
+        <v>0.3193811328585855</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.5295510197084606</v>
+        <v>0.3193809491161264</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.5295506154750507</v>
+        <v>0.3193805448827164</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.5295497702597387</v>
+        <v>0.3193796996674044</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.529549733511247</v>
+        <v>0.3193796629189127</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.5295498805052142</v>
+        <v>0.31937980991288</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.5295498070082306</v>
+        <v>0.3193797364158963</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.5295498805052142</v>
+        <v>0.31937980991288</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.5295499172537061</v>
+        <v>0.3193798466613719</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.5295498070082306</v>
+        <v>0.3193797364158963</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.5295502479901325</v>
+        <v>0.3193801773977983</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.529550137744657</v>
+        <v>0.3193800671523228</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.5295501009961651</v>
+        <v>0.3193800304038308</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.5295500274991815</v>
+        <v>0.3193799569068472</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.5295499907506898</v>
+        <v>0.3193799201583555</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.5295497702597387</v>
+        <v>0.3193796996674044</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.5295496967627551</v>
+        <v>0.3193796261704208</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.5295496232657714</v>
+        <v>0.3193795526734372</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.5295496600142634</v>
+        <v>0.3193795894219291</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.5295495497687878</v>
+        <v>0.3193794791764535</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>1.905315212968727</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.5295496600142634</v>
+        <v>0.3193795894219291</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.905315212968727</v>
+        <v>-0.5195375025212516</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.5295499540021978</v>
+        <v>0.3193798834098636</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM_Base_repeat_4_000008.xlsx
+++ b/out/LSTM_Base_repeat_4_000008.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.2312166209411441</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.305315212968727</v>
+        <v>0.4147854768329915</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.905315212968727</v>
+        <v>1.260787574607127</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.905315212968727</v>
+        <v>0.6147854768329917</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA7" t="n">
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.9209439647931161</v>
+        <v>-0.03121662094114405</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.2312166209411441</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.305315212968727</v>
+        <v>0.4147854768329915</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.905315212968727</v>
+        <v>1.260787574607127</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.905315212968727</v>
+        <v>1.260787574607127</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.905315212968727</v>
+        <v>1.260787574607127</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.905315212968727</v>
+        <v>0.6147854768329917</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA18" t="n">
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.9209439647931161</v>
+        <v>-0.03121662094114405</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.2312166209411441</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.305315212968727</v>
+        <v>0.4147854768329915</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.305315212968727</v>
+        <v>1.060787574607127</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.905315212968727</v>
+        <v>1.260787574607127</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.905315212968727</v>
+        <v>1.260787574607127</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.905315212968727</v>
+        <v>1.260787574607127</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.905315212968727</v>
+        <v>1.260787574607127</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.905315212968727</v>
+        <v>1.260787574607127</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.905315212968727</v>
+        <v>1.260787574607127</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.905315212968727</v>
+        <v>1.260787574607127</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.305315212968727</v>
+        <v>1.260787574607127</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.305315212968727</v>
+        <v>1.060787574607127</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.305315212968727</v>
+        <v>1.060787574607127</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.305315212968727</v>
+        <v>1.060787574607127</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.305315212968727</v>
+        <v>1.060787574607127</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.305315212968727</v>
+        <v>1.060787574607127</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.305315212968727</v>
+        <v>1.060787574607127</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.305315212968727</v>
+        <v>1.060787574607127</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.305315212968727</v>
+        <v>1.060787574607127</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.305315212968727</v>
+        <v>1.060787574607127</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.305315212968727</v>
+        <v>1.060787574607127</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.305315212968727</v>
+        <v>1.060787574607127</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.305315212968727</v>
+        <v>1.060787574607127</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.305315212968727</v>
+        <v>1.060787574607127</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.305315212968727</v>
+        <v>1.060787574607127</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.305315212968727</v>
+        <v>1.060787574607127</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001297736013130052</v>
+        <v>-0.0001241962990622269</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1490849425910108</v>
+        <v>-0.1426776935243748</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.305315212968727</v>
+        <v>0.4147854768329915</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1492147161923238</v>
+        <v>-0.142801889823437</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.2312166209411441</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1492147161923238</v>
+        <v>-0.142801889823437</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1492147161923238</v>
+        <v>-0.142801889823437</v>
       </c>
     </row>
     <row r="49">
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1492147161923238</v>
+        <v>-0.142801889823437</v>
       </c>
     </row>
     <row r="50">
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1492147161923238</v>
+        <v>-0.142801889823437</v>
       </c>
     </row>
     <row r="51">
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1492147161923238</v>
+        <v>-0.142801889823437</v>
       </c>
     </row>
     <row r="52">
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1492147161923238</v>
+        <v>-0.142801889823437</v>
       </c>
     </row>
     <row r="53">
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1492147161923238</v>
+        <v>-0.142801889823437</v>
       </c>
     </row>
     <row r="54">
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.2312166209411441</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1492147161923238</v>
+        <v>-0.142801889823437</v>
       </c>
     </row>
     <row r="55">
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.905315212968727</v>
+        <v>0.6147854768329916</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1492147161923238</v>
+        <v>-0.142801889823437</v>
       </c>
     </row>
     <row r="56">
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.905315212968727</v>
+        <v>1.260787574607127</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1492147161923238</v>
+        <v>-0.142801889823437</v>
       </c>
     </row>
     <row r="57">
@@ -46259,10 +46259,10 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.905315212968727</v>
+        <v>1.260787574607127</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1492147161923238</v>
+        <v>-0.142801889823437</v>
       </c>
     </row>
     <row r="58">
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.905315212968727</v>
+        <v>1.260787574607127</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1492147161923238</v>
+        <v>-0.142801889823437</v>
       </c>
     </row>
     <row r="59">
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.905315212968727</v>
+        <v>1.260787574607127</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1493406846643996</v>
+        <v>-0.1429148713560124</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.4529536807016031</v>
+        <v>0.4062556039119706</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>1.905315212968727</v>
+        <v>1.260787574607127</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.7574368788712351</v>
+        <v>0.6703768765828959</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.03227289123594728</v>
+        <v>0.02894566306922372</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>1.905315212968727</v>
+        <v>1.260787574607127</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.3683018789041531</v>
+        <v>0.3213604059128205</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.05659565517241828</v>
+        <v>0.0507607023051822</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>1.905315212968727</v>
+        <v>0.6147854768329916</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.4492095277998231</v>
+        <v>0.3939267445534526</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.06875703714065395</v>
+        <v>0.0616682585094272</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.2312166209411441</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.5301225618021029</v>
+        <v>0.4664980968442937</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01819466973549165</v>
+        <v>0.01631913132503656</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.2312166209411441</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.4976674099823667</v>
+        <v>0.4373887425777842</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.01010820928558883</v>
+        <v>0.009065557439486982</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.305315212968727</v>
+        <v>0.4147854768329915</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.4996715478632213</v>
+        <v>0.439185742322624</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.02123832524175756</v>
+        <v>0.0190486959761015</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.305315212968727</v>
+        <v>1.060787574607127</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.5320529712864884</v>
+        <v>0.4682287051288656</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.008340508345151199</v>
+        <v>0.007480646071887908</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.905315212968727</v>
+        <v>0.6147854768329917</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.5274782221804594</v>
+        <v>0.4641250873749093</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.005939126475807337</v>
+        <v>0.005325049567685628</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.2312166209411441</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.5310112779026499</v>
+        <v>0.4672931474665543</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.00233464653561096</v>
+        <v>0.002092941902216444</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.5297368183078358</v>
+        <v>0.4661494659514632</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001322156736795153</v>
+        <v>0.001186512378098319</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.5300466643403841</v>
+        <v>0.4664269676358287</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0005011531384238221</v>
+        <v>0.0004483065230431446</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.5297242102800717</v>
+        <v>0.4661372909460834</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.000231706495334477</v>
+        <v>0.0002074853655793212</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.5296872118031967</v>
+        <v>0.4661035592113366</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>8.219113179022926e-05</v>
+        <v>7.331055355233552e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.5296185871245453</v>
+        <v>0.4660414148240294</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>2.075723058958612e-05</v>
+        <v>1.789531607963211e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.5295778273798234</v>
+        <v>0.4660042976478501</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>7.878615294793062e-06</v>
+        <v>6.447658039816054e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.5295728072744883</v>
+        <v>0.4659992797764412</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>1.677971888793091e-06</v>
+        <v>1.164281743501315e-06</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.5295687892301446</v>
+        <v>0.465995189023854</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-1.195152058104458e-07</v>
+        <v>-8.167273192660964e-07</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.5295663545599538</v>
+        <v>0.4659925716204352</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.5295608373179641</v>
+        <v>0.4659870543784455</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.5295545133239562</v>
+        <v>0.4659807303844376</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.5295491455353778</v>
+        <v>0.4659753625958592</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.5295491822838695</v>
+        <v>0.4659753993443509</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.529549292529345</v>
+        <v>0.4659755095898265</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.03121662094114405</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.5295493660263286</v>
+        <v>0.4659755830868101</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.905315212968727</v>
+        <v>0.6147854768329916</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.5295495497687878</v>
+        <v>0.4659757668292692</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.905315212968727</v>
+        <v>1.260787574607127</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.5295510932054442</v>
+        <v>0.4659773102659257</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.905315212968727</v>
+        <v>1.260787574607127</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.5295525631451173</v>
+        <v>0.4659787802055988</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.905315212968727</v>
+        <v>1.260787574607127</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.5295538125938394</v>
+        <v>0.4659800296543208</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.905315212968727</v>
+        <v>1.260787574607127</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.5295551722880367</v>
+        <v>0.4659813893485181</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>1.905315212968727</v>
+        <v>0.6147854768329916</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.5295529673785274</v>
+        <v>0.4659791844390088</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.9209439647931161</v>
+        <v>-0.03121662094114405</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.5295525631451173</v>
+        <v>0.4659787802055988</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.5295517179298054</v>
+        <v>0.4659779349902868</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.5295522691571827</v>
+        <v>0.4659784862176641</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.5295519384207562</v>
+        <v>0.4659781554812377</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.5295516444328218</v>
+        <v>0.4659778614933032</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.5295517179298054</v>
+        <v>0.4659779349902868</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.5295512769479035</v>
+        <v>0.4659774940083849</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.5295511667024279</v>
+        <v>0.4659773837629093</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.5295511299539362</v>
+        <v>0.4659773470144176</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.5295512769479035</v>
+        <v>0.4659774940083849</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.03121662094114405</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.5295507992175098</v>
+        <v>0.4659770162779913</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>1.905315212968727</v>
+        <v>-0.03121662094114405</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.5295517546782971</v>
+        <v>0.4659779717387785</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.9209439647931161</v>
+        <v>-0.03121662094114405</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.5295517179298054</v>
+        <v>0.4659779349902868</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.9209439647931161</v>
+        <v>-0.6772187187152797</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.529551387193379</v>
+        <v>0.4659776042538604</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.6772187187152797</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.5295518281752809</v>
+        <v>0.4659780452357624</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.5295512034509199</v>
+        <v>0.4659774205114013</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.5295510197084606</v>
+        <v>0.4659772367689421</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.5295506154750507</v>
+        <v>0.4659768325355321</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.5295497702597387</v>
+        <v>0.4659759873202201</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.529549733511247</v>
+        <v>0.4659759505717284</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.5295498805052142</v>
+        <v>0.4659760975656956</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.5295498070082306</v>
+        <v>0.465976024068712</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.5295498805052142</v>
+        <v>0.4659760975656956</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.5295499172537061</v>
+        <v>0.4659761343141876</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.5295498070082306</v>
+        <v>0.465976024068712</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.5295502479901325</v>
+        <v>0.465976465050614</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.529550137744657</v>
+        <v>0.4659763548051384</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.5295501009961651</v>
+        <v>0.4659763180566465</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.5295500274991815</v>
+        <v>0.4659762445596629</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.5295499907506898</v>
+        <v>0.4659762078111712</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.5295497702597387</v>
+        <v>0.4659759873202201</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.5295496967627551</v>
+        <v>0.4659759138232365</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.5295496232657714</v>
+        <v>0.4659758403262528</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.8772187187152798</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.5295496600142634</v>
+        <v>0.4659758770747448</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.520943964793116</v>
+        <v>-0.03121662094114405</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.5295495497687878</v>
+        <v>0.4659757668292692</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>1.905315212968727</v>
+        <v>0.6147854768329916</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.5295496600142634</v>
+        <v>0.4659758770747448</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.905315212968727</v>
+        <v>1.260787574607127</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.5295499540021978</v>
+        <v>0.4659761710626792</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM_Base_repeat_4_000008.xlsx
+++ b/out/LSTM_Base_repeat_4_000008.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.009480718523263931</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.8772187187152798</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.00494047999382019</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.2312166209411441</v>
+        <v>-0.5799999999999996</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.002101544290781021</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.4147854768329915</v>
+        <v>-0.16</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.005937940441071987</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.260787574607127</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0.001525298692286015</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.6147854768329917</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.002533536404371262</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.03121662094114405</v>
+        <v>0.3</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.0033328200224787</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.8772187187152798</v>
+        <v>0.16</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.003823863575235009</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.8772187187152798</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.002522439695894718</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.8772187187152798</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.002055425196886063</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.8772187187152798</v>
+        <v>-0.16</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.000535949133336544</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.2312166209411441</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0.0001590894535183907</v>
       </c>
       <c r="JB13" t="n">
-        <v>0.4147854768329915</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.0006152698770165443</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.260787574607127</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.0007947841659188271</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.260787574607127</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.002931890077888966</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.260787574607127</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.001320735551416874</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.6147854768329917</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>-0.0003615822643041611</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.03121662094114405</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>-0.000828249379992485</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.8772187187152798</v>
+        <v>-0.16</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>-0.0005248473025858402</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.2312166209411441</v>
+        <v>-0.3</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>3.234483301639557e-06</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.4147854768329915</v>
+        <v>-0.16</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.0002314061857759953</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.060787574607127</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.0008963616564869881</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.260787574607127</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0.001174633391201496</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.260787574607127</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.002275021746754646</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.260787574607127</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.001938792876899242</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.260787574607127</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.001669898629188538</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.260787574607127</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.001290709711611271</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.260787574607127</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.001644600182771683</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.260787574607127</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.002356971614062786</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.260787574607127</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.003132935613393784</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.060787574607127</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.007620829157531261</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.060787574607127</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0.004486243240535259</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.060787574607127</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.002440331503748894</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.060787574607127</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.001656351611018181</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.060787574607127</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.0005629668012261391</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.060787574607127</v>
+        <v>-0.16</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.001448303461074829</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.060787574607127</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.001002541743218899</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.060787574607127</v>
+        <v>-0.3</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.0008355481550097466</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.060787574607127</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.002691819332540035</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.060787574607127</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.004044363275170326</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.060787574607127</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.003918753005564213</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.060787574607127</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.00509159080684185</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.060787574607127</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.008376547135412693</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.060787574607127</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.009050858207046986</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.060787574607127</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001241962990622269</v>
+        <v>-0.0001100360487170983</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1426776935243748</v>
+        <v>-0.12641028560471</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.001316837966442108</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.4147854768329915</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.142801889823437</v>
+        <v>-0.1265203216534271</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.000819486565887928</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.2312166209411441</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.142801889823437</v>
+        <v>-0.1265203216534271</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.004594057332724333</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.8772187187152798</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.142801889823437</v>
+        <v>-0.1265203216534271</v>
       </c>
     </row>
     <row r="49">
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.004953935742378235</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.8772187187152798</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.142801889823437</v>
+        <v>-0.1265203216534271</v>
       </c>
     </row>
     <row r="50">
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.00491059897467494</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.8772187187152798</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.142801889823437</v>
+        <v>-0.1265203216534271</v>
       </c>
     </row>
     <row r="51">
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.003975328989326954</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.8772187187152798</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.142801889823437</v>
+        <v>-0.1265203216534271</v>
       </c>
     </row>
     <row r="52">
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.003024080768227577</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.8772187187152798</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.142801889823437</v>
+        <v>-0.1265203216534271</v>
       </c>
     </row>
     <row r="53">
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.0008997358381748199</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.8772187187152798</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.142801889823437</v>
+        <v>-0.1265203216534271</v>
       </c>
     </row>
     <row r="54">
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.0003001522272825241</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.2312166209411441</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.142801889823437</v>
+        <v>-0.1265203216534271</v>
       </c>
     </row>
     <row r="55">
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.000164705328643322</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.6147854768329916</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.142801889823437</v>
+        <v>-0.1265203216534271</v>
       </c>
     </row>
     <row r="56">
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.000115332193672657</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.260787574607127</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.142801889823437</v>
+        <v>-0.1265203216534271</v>
       </c>
     </row>
     <row r="57">
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>3.793602809309959e-05</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.260787574607127</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.142801889823437</v>
+        <v>-0.1265203216534271</v>
       </c>
     </row>
     <row r="58">
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.000858774408698082</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.260787574607127</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.142801889823437</v>
+        <v>-0.1265203216534271</v>
       </c>
     </row>
     <row r="59">
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.003982461988925934</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.260787574607127</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1429148713560124</v>
+        <v>-0.1266081103055738</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.4062556039119706</v>
+        <v>0.3156677433322273</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0.001230995170772076</v>
       </c>
       <c r="JB60" t="n">
-        <v>1.260787574607127</v>
+        <v>0.3</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.6703768765828959</v>
+        <v>0.5053339844643211</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.02894566306922372</v>
+        <v>0.02249126043610917</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0.0002521914429962635</v>
       </c>
       <c r="JB61" t="n">
-        <v>1.260787574607127</v>
+        <v>0.3</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.3213604059128205</v>
+        <v>0.234141955313945</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0507607023051822</v>
+        <v>0.03944213587732715</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.001601004041731358</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.6147854768329916</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.3939267445534526</v>
+        <v>0.2905273875796588</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0616682585094272</v>
+        <v>0.04791722522513692</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.00105492677539587</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.2312166209411441</v>
+        <v>0.16</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.4664980968442937</v>
+        <v>0.3469165733611698</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01631913132503656</v>
+        <v>0.0126802633831612</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.00422424403950572</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.2312166209411441</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.4373887425777842</v>
+        <v>0.3242980729237846</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.009065557439486982</v>
+        <v>0.007042988956883369</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.00162025447934866</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.4147854768329915</v>
+        <v>0.3</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.439185742322624</v>
+        <v>0.3256932596693805</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.0190486959761015</v>
+        <v>0.01480027346912595</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.003654483705759048</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.060787574607127</v>
+        <v>0.3</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.4682287051288656</v>
+        <v>0.348260032897355</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.007480646071887908</v>
+        <v>0.00581178661758253</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.001590997911989689</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.6147854768329917</v>
+        <v>0.3</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.4641250873749093</v>
+        <v>0.3450701661974278</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.005325049567685628</v>
+        <v>0.004136569259551194</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.003312484826892614</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.2312166209411441</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.4672931474665543</v>
+        <v>0.3475308204873928</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.002092941902216444</v>
+        <v>0.001625827329813559</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.004558428190648556</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.8772187187152798</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.4661494659514632</v>
+        <v>0.3466409563124818</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001186512378098319</v>
+        <v>0.0009198479002056815</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.007015809882432222</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.8772187187152798</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.4664269676358287</v>
+        <v>0.3468554169121457</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0004483065230431446</v>
+        <v>0.0003473107692045165</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.008523005060851574</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.8772187187152798</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.4661372909460834</v>
+        <v>0.3466290837239938</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0002074853655793212</v>
+        <v>0.0001601440665124258</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.009440221823751926</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.8772187187152798</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.4661035592113366</v>
+        <v>0.3466017369852255</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>7.331055355233552e-05</v>
+        <v>5.554939707654808e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.008934620767831802</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.8772187187152798</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.4660414148240294</v>
+        <v>0.3465522591926719</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>1.789531607963211e-05</v>
+        <v>1.312545856304208e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.007339071482419968</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.8772187187152798</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.4660042976478501</v>
+        <v>0.3465220949278674</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>6.447658039816054e-06</v>
+        <v>4.062729281521043e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.006046334281563759</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.8772187187152798</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.4659992797764412</v>
+        <v>0.3465170807796686</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>1.164281743501315e-06</v>
+        <v>-3.767886923740136e-07</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.003785635577514768</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.8772187187152798</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.465995189023854</v>
+        <v>0.3465127719023512</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-8.167273192660964e-07</v>
+        <v>-1.513939432721747e-06</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.004078296013176441</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.8772187187152798</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.4659925716204352</v>
+        <v>0.3465096042807864</v>
       </c>
     </row>
     <row r="78">
@@ -62943,7 +62943,7 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>-3.128590021429696e-06</v>
+        <v>-3.752393347619798e-06</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.004381549078971148</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.8772187187152798</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.4659870543784455</v>
+        <v>0.3465042349537986</v>
       </c>
     </row>
     <row r="79">
@@ -63738,7 +63738,7 @@
         <v>0</v>
       </c>
       <c r="IY79" t="n">
-        <v>-4.413072433009741e-06</v>
+        <v>-4.70653621650487e-06</v>
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.004495155066251755</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.8772187187152798</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.4659807303844376</v>
+        <v>0.3464982422203682</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.003566230647265911</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.8772187187152798</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.4659753625958592</v>
+        <v>0.3464928744317898</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.002881219610571861</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.8772187187152798</v>
+        <v>0.16</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.4659753993443509</v>
+        <v>0.3464929111802815</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.001914915628731251</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.8772187187152798</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.4659755095898265</v>
+        <v>0.3464930214257571</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.001908853650093079</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.03121662094114405</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.4659755830868101</v>
+        <v>0.3464930949227407</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.001635762862861156</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.6147854768329916</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.4659757668292692</v>
+        <v>0.3464932786651999</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.007227976806461811</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.260787574607127</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.4659773102659257</v>
+        <v>0.3464948221018563</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0.005456198006868362</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.260787574607127</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.4659787802055988</v>
+        <v>0.3464962920415294</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.004402719438076019</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.260787574607127</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.4659800296543208</v>
+        <v>0.3464975414902514</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.01635712385177612</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.260787574607127</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.4659813893485181</v>
+        <v>0.3464989011844488</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.001899589784443378</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.6147854768329916</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.4659791844390088</v>
+        <v>0.3464966962749395</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.007443160749971867</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.03121662094114405</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.4659787802055988</v>
+        <v>0.3464962920415294</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.01332615874707699</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.8772187187152798</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.4659779349902868</v>
+        <v>0.3464954468262175</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.01743717677891254</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.8772187187152798</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.4659784862176641</v>
+        <v>0.3464959980535947</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.01887786015868187</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.8772187187152798</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.4659781554812377</v>
+        <v>0.3464956673171683</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.01644937507808208</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.8772187187152798</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.4659778614933032</v>
+        <v>0.3464953733292339</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.01567607000470161</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.8772187187152798</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.4659779349902868</v>
+        <v>0.3464954468262175</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.01451813895255327</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.8772187187152798</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.4659774940083849</v>
+        <v>0.3464950058443155</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.01300831697881222</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.8772187187152798</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.4659773837629093</v>
+        <v>0.3464948955988399</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.01019911095499992</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.8772187187152798</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.4659773470144176</v>
+        <v>0.3464948588503483</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.00976593978703022</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.8772187187152798</v>
+        <v>0.16</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.4659774940083849</v>
+        <v>0.3464950058443155</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.002127574756741524</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.03121662094114405</v>
+        <v>0.3</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.4659770162779913</v>
+        <v>0.3464945281139219</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.002200046554207802</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.03121662094114405</v>
+        <v>0.3</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.4659779717387785</v>
+        <v>0.3464954835747092</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.005083994939923286</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.03121662094114405</v>
+        <v>0.3</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.4659779349902868</v>
+        <v>0.3464954468262175</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.009480168111622334</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.6772187187152797</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.4659776042538604</v>
+        <v>0.3464951160897911</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.0114061888307333</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.6772187187152797</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.4659780452357624</v>
+        <v>0.346495557071693</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.01258225739002228</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.8772187187152798</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.4659774205114013</v>
+        <v>0.3464949323473319</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.0121681485325098</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.8772187187152798</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.4659772367689421</v>
+        <v>0.3464947486048727</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.01238978654146194</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.8772187187152798</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.4659768325355321</v>
+        <v>0.3464943443714627</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.01183930598199368</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.8772187187152798</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.4659759873202201</v>
+        <v>0.3464934991561507</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.009525977075099945</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.8772187187152798</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.4659759505717284</v>
+        <v>0.346493462407659</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.00770717766135931</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.8772187187152798</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.4659760975656956</v>
+        <v>0.3464936094016263</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.006428588647395372</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.8772187187152798</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.465976024068712</v>
+        <v>0.3464935359046427</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.001683710142970085</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.8772187187152798</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.4659760975656956</v>
+        <v>0.3464936094016263</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.004155935719609261</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.8772187187152798</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.4659761343141876</v>
+        <v>0.3464936461501182</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.002515184227377176</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.8772187187152798</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.465976024068712</v>
+        <v>0.3464935359046427</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.004369122441858053</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.8772187187152798</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.465976465050614</v>
+        <v>0.3464939768865446</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.004583273082971573</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.8772187187152798</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.4659763548051384</v>
+        <v>0.3464938666410691</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.005649290978908539</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.8772187187152798</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.4659763180566465</v>
+        <v>0.3464938298925772</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.00555135402828455</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.8772187187152798</v>
+        <v>-0.16</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.4659762445596629</v>
+        <v>0.3464937563955935</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.005613041110336781</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.8772187187152798</v>
+        <v>-0.16</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.4659762078111712</v>
+        <v>0.3464937196471018</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.005965379998087883</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.8772187187152798</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.4659759873202201</v>
+        <v>0.3464934991561507</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.004390895366668701</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.8772187187152798</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.4659759138232365</v>
+        <v>0.3464934256591671</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.004047266207635403</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.8772187187152798</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.4659758403262528</v>
+        <v>0.3464933521621835</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.004023159388452768</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.8772187187152798</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.4659758770747448</v>
+        <v>0.3464933889106754</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.002707868814468384</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.03121662094114405</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.4659757668292692</v>
+        <v>0.3464932786651999</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0.0003461837768554688</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.6147854768329916</v>
+        <v>0.9999999999999996</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.4659758770747448</v>
+        <v>0.3464933889106754</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0.001040411181747913</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.260787574607127</v>
+        <v>0.9999999999999996</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.4659761710626792</v>
+        <v>0.3464936828986099</v>
       </c>
     </row>
   </sheetData>
